--- a/GIL.xlsx
+++ b/GIL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4054B1B3-E34E-41CE-B7F3-E8C61ABEB2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EC72C4-224A-49E2-9408-E8B37A9731E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{8FF81416-71A4-47E4-A621-F1E8D8B5CE92}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{8FF81416-71A4-47E4-A621-F1E8D8B5CE92}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>Gildan Activewear</t>
   </si>
@@ -193,6 +193,9 @@
   </si>
   <si>
     <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -653,7 +656,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>60</v>
+        <v>63.14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -661,10 +664,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>149.22999999999999</v>
+        <v>186.15799999999999</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -676,7 +679,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>8953.7999999999993</v>
+        <v>11754.016119999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -687,10 +690,10 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>112.633</v>
+        <v>237.05500000000001</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -698,11 +701,11 @@
         <v>8</v>
       </c>
       <c r="I6" s="3">
-        <f>1304.22+450</f>
-        <v>1754.22</v>
+        <f>450+4265.1</f>
+        <v>4715.1000000000004</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -711,7 +714,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4+I6-I5</f>
-        <v>10595.386999999999</v>
+        <v>16232.061119999998</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +777,9 @@
       <c r="N2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="4"/>
+      <c r="O2" s="11" t="s">
+        <v>52</v>
+      </c>
       <c r="Q2" s="4" t="s">
         <v>19</v>
       </c>
@@ -944,7 +949,9 @@
         <v>819.5</v>
       </c>
       <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="O5" s="3">
+        <v>1069.0999999999999</v>
+      </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -1035,7 +1042,9 @@
         <v>30.8</v>
       </c>
       <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="O6" s="3">
+        <v>25</v>
+      </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -1126,7 +1135,9 @@
         <v>60.3</v>
       </c>
       <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
+      <c r="O7" s="3">
+        <v>71.900000000000006</v>
+      </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
@@ -1223,7 +1234,9 @@
         <v>910.6</v>
       </c>
       <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
+      <c r="O8" s="6">
+        <v>1166</v>
+      </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
@@ -1314,7 +1327,9 @@
         <v>603.97</v>
       </c>
       <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
+      <c r="O9" s="3">
+        <v>887.59</v>
+      </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -1408,7 +1423,7 @@
         <v>277.60699999999997</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" ref="J10:N10" si="1">+J8-J9</f>
+        <f t="shared" ref="J10:O10" si="1">+J8-J9</f>
         <v>821.5</v>
       </c>
       <c r="K10" s="3">
@@ -1427,7 +1442,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O10" s="3"/>
+      <c r="O10" s="3">
+        <f t="shared" si="1"/>
+        <v>278.40999999999997</v>
+      </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -1518,7 +1536,9 @@
         <v>95.26</v>
       </c>
       <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="O11" s="3">
+        <v>218.654</v>
+      </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -1609,7 +1629,9 @@
         <v>19.231999999999999</v>
       </c>
       <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="O12" s="3">
+        <v>60.976999999999997</v>
+      </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -1703,7 +1725,7 @@
         <v>192.94499999999996</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" ref="J13:N13" si="3">+J10-SUM(J11:J12)</f>
+        <f t="shared" ref="J13:O13" si="3">+J10-SUM(J11:J12)</f>
         <v>821.5</v>
       </c>
       <c r="K13" s="3">
@@ -1722,7 +1744,10 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
+      <c r="O13" s="3">
+        <f t="shared" si="3"/>
+        <v>-1.2210000000000036</v>
+      </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
@@ -1813,7 +1838,9 @@
         <v>43.707999999999998</v>
       </c>
       <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="O14" s="3">
+        <v>66.733999999999995</v>
+      </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
@@ -1907,7 +1934,7 @@
         <v>162.72799999999995</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" ref="J15:N15" si="5">+J13-J14</f>
+        <f t="shared" ref="J15:O15" si="5">+J13-J14</f>
         <v>821.5</v>
       </c>
       <c r="K15" s="3">
@@ -1926,7 +1953,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
+      <c r="O15" s="3">
+        <f t="shared" si="5"/>
+        <v>-67.954999999999998</v>
+      </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
@@ -2017,7 +2047,10 @@
         <v>28.242000000000001</v>
       </c>
       <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
+      <c r="O16" s="3">
+        <f>-12.959+10.737</f>
+        <v>-2.2219999999999995</v>
+      </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -2111,7 +2144,7 @@
         <v>131.47399999999996</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" ref="J17:N17" si="7">+J15-J16</f>
+        <f t="shared" ref="J17:O17" si="7">+J15-J16</f>
         <v>821.5</v>
       </c>
       <c r="K17" s="3">
@@ -2130,7 +2163,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="O17" s="3"/>
+      <c r="O17" s="3">
+        <f t="shared" si="7"/>
+        <v>-65.733000000000004</v>
+      </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -2270,7 +2306,7 @@
         <v>41</v>
       </c>
       <c r="C19" s="7" t="e">
-        <f t="shared" ref="C19:N19" si="8">+C17/C20</f>
+        <f t="shared" ref="C19:O19" si="8">+C17/C20</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D19" s="7" t="e">
@@ -2317,7 +2353,10 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O19" s="3"/>
+      <c r="O19" s="7">
+        <f t="shared" si="8"/>
+        <v>-0.35310327786074197</v>
+      </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -2408,7 +2447,9 @@
         <v>149.22999999999999</v>
       </c>
       <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
+      <c r="O20" s="3">
+        <v>186.15799999999999</v>
+      </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
@@ -2576,14 +2617,17 @@
         <v>0.11636116768499671</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" ref="M22:N22" si="11">+M3/I3-1</f>
+        <f t="shared" ref="M22:O22" si="11">+M3/I3-1</f>
         <v>5.3659774197640564E-2</v>
       </c>
       <c r="N22" s="9" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O22" s="3"/>
+      <c r="O22" s="9">
+        <f t="shared" si="11"/>
+        <v>-1</v>
+      </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
@@ -2677,14 +2721,17 @@
         <v>-0.23328025477707004</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" ref="M23:N23" si="13">+M4/I4-1</f>
+        <f t="shared" ref="M23:O23" si="13">+M4/I4-1</f>
         <v>-0.22178988326848248</v>
       </c>
       <c r="N23" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O23" s="3"/>
+      <c r="O23" s="9">
+        <f t="shared" si="13"/>
+        <v>-1</v>
+      </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
@@ -2779,14 +2826,17 @@
         <v>6.529807469264659E-2</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" ref="M24:N24" si="15">+M8/I8-1</f>
+        <f t="shared" ref="M24:O24" si="15">+M8/I8-1</f>
         <v>2.1876185324753772E-2</v>
       </c>
       <c r="N24" s="10">
         <f t="shared" si="15"/>
         <v>-1</v>
       </c>
-      <c r="O24" s="6"/>
+      <c r="O24" s="10">
+        <f>+O8/K8-1</f>
+        <v>0.63839521577355862</v>
+      </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2899,7 +2949,10 @@
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O25" s="3"/>
+      <c r="O25" s="9">
+        <f t="shared" ref="O25" si="18">+O10/O8</f>
+        <v>0.23877358490566036</v>
+      </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
@@ -2965,39 +3018,39 @@
         <v>50</v>
       </c>
       <c r="C26" s="9" t="e">
-        <f t="shared" ref="C26:K26" si="18">+C13/C8</f>
+        <f t="shared" ref="C26:K26" si="19">+C13/C8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.17820188734120318</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.15104570879970569</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.16382161911389473</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.21652306235172916</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.18217100012365248</v>
       </c>
       <c r="L26" s="9">
@@ -3005,14 +3058,17 @@
         <v>0.21719107240065322</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" ref="M26:N26" si="19">+M13/M8</f>
+        <f t="shared" ref="M26:N26" si="20">+M13/M8</f>
         <v>0.21100153744783656</v>
       </c>
       <c r="N26" s="9" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O26" s="3"/>
+      <c r="O26" s="9">
+        <f t="shared" ref="O26" si="21">+O13/O8</f>
+        <v>-1.0471698113207579E-3</v>
+      </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
@@ -3078,39 +3134,39 @@
         <v>51</v>
       </c>
       <c r="C27" s="9" t="e">
-        <f t="shared" ref="C27:K27" si="20">+C16/C15</f>
+        <f t="shared" ref="C27:K27" si="22">+C16/C15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>5.141133536903255E-2</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4.4967282174551704E-2</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.50042316734344927</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.19206282876948041</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.15132989918021283</v>
       </c>
       <c r="L27" s="9">
@@ -3118,14 +3174,17 @@
         <v>0.17655733202784513</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" ref="M27:N27" si="21">+M16/M15</f>
+        <f t="shared" ref="M27:N27" si="23">+M16/M15</f>
         <v>0.19027150845516408</v>
       </c>
       <c r="N27" s="9" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O27" s="3"/>
+      <c r="O27" s="9">
+        <f t="shared" ref="O27" si="24">+O16/O15</f>
+        <v>3.269810904274887E-2</v>
+      </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
